--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1979</v>
+        <v>-0.5715</v>
       </c>
       <c r="E2">
-        <v>0.2265</v>
+        <v>-0.011</v>
       </c>
       <c r="F2">
-        <v>0.02302</v>
+        <v>0.06890000000000002</v>
       </c>
       <c r="G2">
-        <v>0.06359212055006563</v>
+        <v>2.91809733816349</v>
       </c>
       <c r="H2">
-        <v>0.06359212055006563</v>
+        <v>2.91809733816349</v>
       </c>
       <c r="I2">
-        <v>0.06009533915768705</v>
+        <v>1.144222187221085</v>
       </c>
       <c r="J2">
-        <v>0.04853894627387636</v>
+        <v>1.038534081816715</v>
       </c>
       <c r="K2">
-        <v>191.4000000000002</v>
+        <v>3143.5</v>
       </c>
       <c r="L2">
-        <v>0.001660713030697163</v>
+        <v>1.650391137711976</v>
       </c>
       <c r="M2">
-        <v>2714.3</v>
+        <v>3036.206</v>
       </c>
       <c r="N2">
-        <v>0.03323940626335584</v>
+        <v>0.04753973510452239</v>
       </c>
       <c r="O2">
-        <v>14.18129571577846</v>
+        <v>0.9658679815492286</v>
       </c>
       <c r="P2">
-        <v>2679.8</v>
+        <v>2537.2</v>
       </c>
       <c r="Q2">
-        <v>0.03281691813894594</v>
+        <v>0.0397264928358597</v>
       </c>
       <c r="R2">
-        <v>14.0010449320794</v>
+        <v>0.807125815174169</v>
       </c>
       <c r="S2">
-        <v>34.5</v>
+        <v>499.0060000000001</v>
       </c>
       <c r="T2">
-        <v>0.01271045941863464</v>
+        <v>0.1643518259301247</v>
       </c>
       <c r="U2">
-        <v>44806.7</v>
+        <v>51648.2</v>
       </c>
       <c r="V2">
-        <v>0.5487043085216468</v>
+        <v>0.8086874693697969</v>
       </c>
       <c r="W2">
-        <v>-0.05346934908252535</v>
+        <v>-0.06250749850029994</v>
       </c>
       <c r="X2">
-        <v>0.08659139429282242</v>
+        <v>0.1257048381800152</v>
       </c>
       <c r="Y2">
-        <v>-0.1400607433753478</v>
+        <v>-0.1882123366803151</v>
       </c>
       <c r="Z2">
-        <v>1.228203833005107</v>
+        <v>0.02217198625935183</v>
       </c>
       <c r="AA2">
-        <v>0.05348737437647847</v>
+        <v>-0.09105143662412904</v>
       </c>
       <c r="AB2">
-        <v>0.06120021322448158</v>
+        <v>0.09049977469542371</v>
       </c>
       <c r="AC2">
-        <v>-0.008821657785233875</v>
+        <v>-0.1815512113195528</v>
       </c>
       <c r="AD2">
-        <v>88723.10000000001</v>
+        <v>77762.39999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>88723.10000000001</v>
+        <v>77762.39999999999</v>
       </c>
       <c r="AG2">
-        <v>43916.40000000001</v>
+        <v>26114.19999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5207298649741581</v>
+        <v>0.5490566557296488</v>
       </c>
       <c r="AI2">
-        <v>0.668068970138993</v>
+        <v>0.654984670327819</v>
       </c>
       <c r="AJ2">
-        <v>0.3497210841286716</v>
+        <v>0.2902193687771515</v>
       </c>
       <c r="AK2">
-        <v>0.4990579395581294</v>
+        <v>0.3893237203283448</v>
       </c>
       <c r="AL2">
-        <v>1238.28</v>
+        <v>1004.8</v>
       </c>
       <c r="AM2">
-        <v>1238.28</v>
+        <v>1004.8</v>
       </c>
       <c r="AN2">
-        <v>12.18071362868793</v>
+        <v>32.06961398878258</v>
       </c>
       <c r="AO2">
-        <v>5.59331492069645</v>
+        <v>2.168988853503185</v>
       </c>
       <c r="AP2">
-        <v>6.029242576092479</v>
+        <v>10.76963048498845</v>
       </c>
       <c r="AQ2">
-        <v>5.59331492069645</v>
+        <v>2.168988853503185</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chesnara plc (LSE:CSN)</t>
+          <t>Prudential plc (LSE:PRU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.499</v>
+        <v>-0.545</v>
       </c>
       <c r="E3">
-        <v>0.307</v>
+        <v>-0.09039999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.09300000000000001</v>
       </c>
       <c r="G3">
-        <v>0.03361863584223065</v>
+        <v>1.641751201281367</v>
       </c>
       <c r="H3">
-        <v>0.03361863584223065</v>
+        <v>1.641751201281367</v>
       </c>
       <c r="I3">
-        <v>0.04451601517691697</v>
+        <v>0.9733048585157501</v>
       </c>
       <c r="J3">
-        <v>0.03742182949135252</v>
+        <v>0.7194743188318674</v>
       </c>
       <c r="K3">
-        <v>63.3</v>
+        <v>2072</v>
       </c>
       <c r="L3">
-        <v>0.02792729197917586</v>
+        <v>1.106246663107314</v>
       </c>
       <c r="M3">
-        <v>45.5</v>
+        <v>458</v>
       </c>
       <c r="N3">
-        <v>0.07852951328960994</v>
+        <v>0.01231772192070399</v>
       </c>
       <c r="O3">
-        <v>0.7187993680884677</v>
+        <v>0.221042471042471</v>
       </c>
       <c r="P3">
-        <v>45.5</v>
+        <v>458</v>
       </c>
       <c r="Q3">
-        <v>0.07852951328960994</v>
+        <v>0.01231772192070399</v>
       </c>
       <c r="R3">
-        <v>0.7187993680884677</v>
+        <v>0.221042471042471</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>100.3</v>
+        <v>6415</v>
       </c>
       <c r="V3">
-        <v>0.1731101139109424</v>
+        <v>0.1725287906578954</v>
       </c>
       <c r="W3">
-        <v>0.1087442020271431</v>
+        <v>0.1318653344364539</v>
       </c>
       <c r="X3">
-        <v>0.06588893205479818</v>
+        <v>0.1012288982310274</v>
       </c>
       <c r="Y3">
-        <v>0.04285526997234491</v>
+        <v>0.03063643620542647</v>
       </c>
       <c r="Z3">
-        <v>5.205787781350482</v>
+        <v>0.115710137764873</v>
       </c>
       <c r="AA3">
-        <v>0.1948101027218641</v>
+        <v>0.08325047255032357</v>
       </c>
       <c r="AB3">
-        <v>0.06086096191959772</v>
+        <v>0.09354151678189768</v>
       </c>
       <c r="AC3">
-        <v>0.1339491408022664</v>
+        <v>-0.01029104423157411</v>
       </c>
       <c r="AD3">
-        <v>77.09999999999999</v>
+        <v>5919</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>77.09999999999999</v>
+        <v>5919</v>
       </c>
       <c r="AG3">
-        <v>-23.2</v>
+        <v>-496</v>
       </c>
       <c r="AH3">
-        <v>0.1174409748667174</v>
+        <v>0.1373279630265515</v>
       </c>
       <c r="AI3">
-        <v>0.1065947739527167</v>
+        <v>0.2667297553062052</v>
       </c>
       <c r="AJ3">
-        <v>-0.04171161452714852</v>
+        <v>-0.01352007021713887</v>
       </c>
       <c r="AK3">
-        <v>-0.03723916532905298</v>
+        <v>-0.03144016227180527</v>
       </c>
       <c r="AL3">
-        <v>2.78</v>
+        <v>267</v>
       </c>
       <c r="AM3">
-        <v>2.78</v>
+        <v>267</v>
       </c>
       <c r="AN3">
-        <v>0.7558823529411764</v>
+        <v>3.175429184549356</v>
       </c>
       <c r="AO3">
-        <v>36.29496402877698</v>
+        <v>6.827715355805243</v>
       </c>
       <c r="AP3">
-        <v>-0.2274509803921569</v>
+        <v>-0.2660944206008584</v>
       </c>
       <c r="AQ3">
-        <v>36.29496402877698</v>
+        <v>6.827715355805243</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prudential plc (LSE:PRU)</t>
+          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -858,122 +861,107 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0604</v>
+      <c r="E4">
+        <v>0.0684</v>
       </c>
       <c r="F4">
-        <v>0.151</v>
-      </c>
-      <c r="G4">
-        <v>0.04890533338445611</v>
-      </c>
-      <c r="H4">
-        <v>0.04890533338445611</v>
-      </c>
-      <c r="I4">
-        <v>0.05477167286530425</v>
-      </c>
-      <c r="J4">
-        <v>0.04826432886691635</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="K4">
-        <v>-2404</v>
-      </c>
-      <c r="L4">
-        <v>-0.04608718990836241</v>
+        <v>2598</v>
       </c>
       <c r="M4">
-        <v>423</v>
+        <v>1444.8</v>
       </c>
       <c r="N4">
-        <v>0.008968761992803788</v>
+        <v>0.08104060443905971</v>
       </c>
       <c r="O4">
-        <v>-0.1759567387687188</v>
+        <v>0.5561200923787529</v>
       </c>
       <c r="P4">
-        <v>423</v>
+        <v>1371.9</v>
       </c>
       <c r="Q4">
-        <v>0.008968761992803788</v>
+        <v>0.07695155400743771</v>
       </c>
       <c r="R4">
-        <v>-0.1759567387687188</v>
+        <v>0.5280600461893765</v>
       </c>
       <c r="S4">
+        <v>72.90000000000009</v>
+      </c>
+      <c r="T4">
+        <v>0.0504568106312293</v>
+      </c>
+      <c r="U4">
+        <v>30103.9</v>
+      </c>
+      <c r="V4">
+        <v>1.688564681598151</v>
+      </c>
+      <c r="W4">
+        <v>0.181800369478811</v>
+      </c>
+      <c r="X4">
+        <v>0.2446460460594309</v>
+      </c>
+      <c r="Y4">
+        <v>-0.06284567658061996</v>
+      </c>
+      <c r="Z4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>6295</v>
-      </c>
-      <c r="V4">
-        <v>0.1334712925406616</v>
-      </c>
-      <c r="W4">
-        <v>-0.1257980115122972</v>
-      </c>
-      <c r="X4">
-        <v>0.06700623068623393</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1928042421985312</v>
-      </c>
-      <c r="Z4">
-        <v>1.889037772063883</v>
-      </c>
       <c r="AA4">
-        <v>0.09117314027291823</v>
+        <v>0.04464741953402325</v>
       </c>
       <c r="AB4">
-        <v>0.06120021322448158</v>
+        <v>0.08871137804719656</v>
       </c>
       <c r="AC4">
-        <v>0.02997292704843665</v>
+        <v>-0.04406395851317331</v>
       </c>
       <c r="AD4">
-        <v>7695</v>
+        <v>63966.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7695</v>
+        <v>63966.2</v>
       </c>
       <c r="AG4">
-        <v>1400</v>
+        <v>33862.3</v>
       </c>
       <c r="AH4">
-        <v>0.1402694558930489</v>
+        <v>0.7820373791327758</v>
       </c>
       <c r="AI4">
-        <v>0.3217242244334811</v>
+        <v>0.8188816103622778</v>
       </c>
       <c r="AJ4">
-        <v>0.02882811647382716</v>
+        <v>0.6550984322040456</v>
       </c>
       <c r="AK4">
-        <v>0.07944163876751972</v>
+        <v>0.7053147039587421</v>
       </c>
       <c r="AL4">
-        <v>348</v>
+        <v>275.8</v>
       </c>
       <c r="AM4">
-        <v>348</v>
+        <v>275.8</v>
       </c>
       <c r="AN4">
-        <v>2.467928159076331</v>
+        <v>16.7564834704249</v>
       </c>
       <c r="AO4">
-        <v>8.209770114942529</v>
+        <v>13.22661348803481</v>
       </c>
       <c r="AP4">
-        <v>0.4490057729313663</v>
+        <v>8.870513962382772</v>
       </c>
       <c r="AQ4">
-        <v>8.209770114942529</v>
+        <v>13.22661348803481</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
+          <t>Just Group plc (LSE:JUST)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,124 +981,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0472</v>
-      </c>
-      <c r="E5">
-        <v>0.146</v>
+        <v>-0.598</v>
       </c>
       <c r="F5">
-        <v>0.039</v>
+        <v>0.0958</v>
       </c>
       <c r="G5">
-        <v>0.151851448222416</v>
+        <v>5.034700315457413</v>
       </c>
       <c r="H5">
-        <v>0.151851448222416</v>
+        <v>5.034700315457413</v>
       </c>
       <c r="I5">
-        <v>0.2395681972294876</v>
+        <v>-3.668769716088328</v>
       </c>
       <c r="J5">
-        <v>0.1956472480530209</v>
+        <v>-3.668769716088328</v>
       </c>
       <c r="K5">
-        <v>3289.8</v>
+        <v>-208.4</v>
       </c>
       <c r="L5">
-        <v>0.1991790177274048</v>
+        <v>-6.574132492113565</v>
       </c>
       <c r="M5">
-        <v>1510.9</v>
+        <v>462.7</v>
       </c>
       <c r="N5">
-        <v>0.06319589094954869</v>
+        <v>0.4531387719126432</v>
       </c>
       <c r="O5">
-        <v>0.4592680406103715</v>
+        <v>-2.220249520153551</v>
       </c>
       <c r="P5">
-        <v>1476.4</v>
+        <v>36.7</v>
       </c>
       <c r="Q5">
-        <v>0.06175287139977079</v>
+        <v>0.03594163157379297</v>
       </c>
       <c r="R5">
-        <v>0.448781080916773</v>
+        <v>-0.1761036468330134</v>
       </c>
       <c r="S5">
-        <v>34.5</v>
+        <v>426</v>
       </c>
       <c r="T5">
-        <v>0.02283407240717453</v>
+        <v>0.9206829479144154</v>
       </c>
       <c r="U5">
-        <v>22646.2</v>
+        <v>1826.5</v>
       </c>
       <c r="V5">
-        <v>0.9472147631356606</v>
+        <v>1.788757222603075</v>
       </c>
       <c r="W5">
-        <v>0.2824468770122344</v>
+        <v>-0.06250749850029994</v>
       </c>
       <c r="X5">
-        <v>0.1754684083216748</v>
+        <v>0.1831866056932369</v>
       </c>
       <c r="Y5">
-        <v>0.1069784686905596</v>
+        <v>-0.2456941041935368</v>
       </c>
       <c r="Z5">
-        <v>0.2733867964346897</v>
+        <v>0.02481797541689502</v>
       </c>
       <c r="AA5">
-        <v>0.05348737437647847</v>
+        <v>-0.09105143662412904</v>
       </c>
       <c r="AB5">
-        <v>0.06230903216171235</v>
+        <v>0.09049977469542371</v>
       </c>
       <c r="AC5">
-        <v>-0.008821657785233875</v>
+        <v>-0.1815512113195528</v>
       </c>
       <c r="AD5">
-        <v>73728.3</v>
+        <v>2163.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>73728.3</v>
+        <v>2163.3</v>
       </c>
       <c r="AG5">
-        <v>51082.10000000001</v>
+        <v>336.8000000000002</v>
       </c>
       <c r="AH5">
-        <v>0.7551305095942604</v>
+        <v>0.6793430473558598</v>
       </c>
       <c r="AI5">
-        <v>0.8380901607105914</v>
+        <v>0.4475916577009021</v>
       </c>
       <c r="AJ5">
-        <v>0.6811827663044421</v>
+        <v>0.2480300463951691</v>
       </c>
       <c r="AK5">
-        <v>0.7819614362516379</v>
+        <v>0.1120164964911698</v>
       </c>
       <c r="AL5">
-        <v>339.8</v>
+        <v>163.7</v>
       </c>
       <c r="AM5">
-        <v>339.8</v>
+        <v>163.7</v>
       </c>
       <c r="AN5">
-        <v>18.42700757291745</v>
+        <v>-18.79496090356212</v>
       </c>
       <c r="AO5">
-        <v>11.64479105356092</v>
+        <v>-0.710445937690898</v>
       </c>
       <c r="AP5">
-        <v>12.76701407113044</v>
+        <v>-2.926151172893138</v>
       </c>
       <c r="AQ5">
-        <v>11.64479105356092</v>
+        <v>-0.710445937690898</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Just Group plc (LSE:JUST)</t>
+          <t>Chesnara plc (LSE:CSN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1129,119 +1114,101 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="F6">
-        <v>0.007039999999999999</v>
-      </c>
-      <c r="G6">
-        <v>0.1347501057877663</v>
-      </c>
-      <c r="H6">
-        <v>0.1347501057877663</v>
-      </c>
-      <c r="I6">
-        <v>0.004278527434294042</v>
-      </c>
-      <c r="J6">
-        <v>0.004278527434294042</v>
-      </c>
       <c r="K6">
-        <v>-169.3</v>
-      </c>
-      <c r="L6">
-        <v>-0.03979970849593305</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="M6">
-        <v>38.8</v>
+        <v>41.306</v>
       </c>
       <c r="N6">
-        <v>0.03300442327322219</v>
+        <v>0.08042445482866044</v>
       </c>
       <c r="O6">
-        <v>-0.2291789722386296</v>
+        <v>-0.578515406162465</v>
       </c>
       <c r="P6">
-        <v>38.8</v>
+        <v>41.2</v>
       </c>
       <c r="Q6">
-        <v>0.03300442327322219</v>
+        <v>0.08021806853582555</v>
       </c>
       <c r="R6">
-        <v>-0.2291789722386296</v>
+        <v>-0.5770308123249299</v>
       </c>
       <c r="S6">
+        <v>0.1060000000000016</v>
+      </c>
+      <c r="T6">
+        <v>0.002566213140948086</v>
+      </c>
+      <c r="U6">
+        <v>254.6</v>
+      </c>
+      <c r="V6">
+        <v>0.4957165109034268</v>
+      </c>
+      <c r="W6">
+        <v>-0.1104921077065924</v>
+      </c>
+      <c r="X6">
+        <v>0.1160706332365033</v>
+      </c>
+      <c r="Y6">
+        <v>-0.2265627409430957</v>
+      </c>
+      <c r="Z6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>3180.4</v>
-      </c>
-      <c r="V6">
-        <v>2.705341953045254</v>
-      </c>
-      <c r="W6">
-        <v>-0.05346934908252535</v>
-      </c>
-      <c r="X6">
-        <v>0.0964440536053898</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1499134026879151</v>
-      </c>
-      <c r="Z6">
-        <v>2.209307156954399</v>
-      </c>
       <c r="AA6">
-        <v>0.00945258128181157</v>
+        <v>-0.1892455858747993</v>
       </c>
       <c r="AB6">
-        <v>0.062416158454539</v>
+        <v>0.09057541633748657</v>
       </c>
       <c r="AC6">
-        <v>-0.05296357717272743</v>
+        <v>-0.2798210022122859</v>
       </c>
       <c r="AD6">
-        <v>1123.7</v>
+        <v>264</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1123.7</v>
+        <v>264</v>
       </c>
       <c r="AG6">
-        <v>-2056.7</v>
+        <v>9.400000000000006</v>
       </c>
       <c r="AH6">
-        <v>0.4887139564215195</v>
+        <v>0.3395061728395062</v>
       </c>
       <c r="AI6">
-        <v>0.2522674209770115</v>
+        <v>0.3699033207229928</v>
       </c>
       <c r="AJ6">
-        <v>2.334241289297469</v>
+        <v>0.01797323135755259</v>
       </c>
       <c r="AK6">
-        <v>-1.61436420722135</v>
+        <v>0.02047484208233501</v>
       </c>
       <c r="AL6">
-        <v>201</v>
+        <v>12.7</v>
       </c>
       <c r="AM6">
-        <v>201</v>
+        <v>12.7</v>
       </c>
       <c r="AN6">
-        <v>52.50934579439253</v>
+        <v>-2.256410256410256</v>
       </c>
       <c r="AO6">
-        <v>0.09054726368159204</v>
+        <v>-9.283464566929135</v>
       </c>
       <c r="AP6">
-        <v>-96.10747663551402</v>
+        <v>-0.08034188034188039</v>
       </c>
       <c r="AQ6">
-        <v>0.09054726368159204</v>
+        <v>-9.283464566929135</v>
       </c>
     </row>
     <row r="7">
@@ -1260,47 +1227,29 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.4429999999999999</v>
-      </c>
       <c r="F7">
-        <v>-0.1</v>
-      </c>
-      <c r="G7">
-        <v>0.04046189376443417</v>
-      </c>
-      <c r="H7">
-        <v>0.04046189376443417</v>
-      </c>
-      <c r="I7">
-        <v>-0.0001725235628237938</v>
-      </c>
-      <c r="J7">
-        <v>-8.626178141189689e-05</v>
+        <v>-0.027</v>
       </c>
       <c r="K7">
-        <v>-588.4</v>
-      </c>
-      <c r="L7">
-        <v>-0.01469071843205792</v>
+        <v>-1246.7</v>
       </c>
       <c r="M7">
-        <v>696.1</v>
+        <v>629.4</v>
       </c>
       <c r="N7">
-        <v>0.07881388555512782</v>
+        <v>0.08596364232350411</v>
       </c>
       <c r="O7">
-        <v>-1.183038749150238</v>
+        <v>-0.5048528114221544</v>
       </c>
       <c r="P7">
-        <v>696.1</v>
+        <v>629.4</v>
       </c>
       <c r="Q7">
-        <v>0.07881388555512782</v>
+        <v>0.08596364232350411</v>
       </c>
       <c r="R7">
-        <v>-1.183038749150238</v>
+        <v>-0.5048528114221544</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1309,73 +1258,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>12584.8</v>
+        <v>13048.2</v>
       </c>
       <c r="V7">
-        <v>1.424877154049953</v>
+        <v>1.782127101629403</v>
       </c>
       <c r="W7">
-        <v>-0.08454265927181814</v>
+        <v>-0.1369352943114792</v>
       </c>
       <c r="X7">
-        <v>0.08659139429282242</v>
+        <v>0.1257048381800152</v>
       </c>
       <c r="Y7">
-        <v>-0.1711340535646406</v>
+        <v>-0.2626401324914944</v>
       </c>
       <c r="Z7">
-        <v>11.61514369399414</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>-0.001001942986399095</v>
+        <v>-1.203756201275691</v>
       </c>
       <c r="AB7">
-        <v>0.06064711456276981</v>
+        <v>0.08954917188445799</v>
       </c>
       <c r="AC7">
-        <v>-0.0616490575491689</v>
+        <v>-1.293305373160149</v>
       </c>
       <c r="AD7">
-        <v>6099</v>
+        <v>5449.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>6099</v>
+        <v>5449.9</v>
       </c>
       <c r="AG7">
-        <v>-6485.799999999999</v>
+        <v>-7598.300000000001</v>
       </c>
       <c r="AH7">
-        <v>0.4084735319331333</v>
+        <v>0.4267202229947696</v>
       </c>
       <c r="AI7">
-        <v>0.3875382836228698</v>
+        <v>0.4233918582970789</v>
       </c>
       <c r="AJ7">
-        <v>-2.76414933515172</v>
+        <v>27.47035430224138</v>
       </c>
       <c r="AK7">
-        <v>-2.057025055502696</v>
+        <v>43.12315550510766</v>
       </c>
       <c r="AL7">
-        <v>346.7</v>
+        <v>285.6</v>
       </c>
       <c r="AM7">
-        <v>346.7</v>
+        <v>285.6</v>
       </c>
       <c r="AN7">
-        <v>147.3188405797102</v>
+        <v>-1.801917672342536</v>
       </c>
       <c r="AO7">
-        <v>-0.01993077588693395</v>
+        <v>-10.70483193277311</v>
       </c>
       <c r="AP7">
-        <v>-156.6618357487923</v>
+        <v>2.512249958670855</v>
       </c>
       <c r="AQ7">
-        <v>-0.01993077588693395</v>
+        <v>-10.70483193277311</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
@@ -587,125 +587,107 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.5715</v>
-      </c>
       <c r="E2">
-        <v>-0.011</v>
+        <v>0.0344</v>
       </c>
       <c r="F2">
-        <v>0.06890000000000002</v>
-      </c>
-      <c r="G2">
-        <v>2.91809733816349</v>
-      </c>
-      <c r="H2">
-        <v>2.91809733816349</v>
-      </c>
-      <c r="I2">
-        <v>1.144222187221085</v>
-      </c>
-      <c r="J2">
-        <v>1.038534081816715</v>
+        <v>0.107</v>
       </c>
       <c r="K2">
-        <v>3143.5</v>
-      </c>
-      <c r="L2">
-        <v>1.650391137711976</v>
+        <v>4988.8</v>
       </c>
       <c r="M2">
-        <v>3036.206</v>
+        <v>2816.8</v>
       </c>
       <c r="N2">
-        <v>0.04753973510452239</v>
+        <v>0.04826949209760143</v>
       </c>
       <c r="O2">
-        <v>0.9658679815492286</v>
+        <v>0.5646247594611929</v>
       </c>
       <c r="P2">
-        <v>2537.2</v>
+        <v>2788.8</v>
       </c>
       <c r="Q2">
-        <v>0.0397264928358597</v>
+        <v>0.04778967607277438</v>
       </c>
       <c r="R2">
-        <v>0.807125815174169</v>
+        <v>0.5590121872995509</v>
       </c>
       <c r="S2">
-        <v>499.0060000000001</v>
+        <v>28</v>
       </c>
       <c r="T2">
-        <v>0.1643518259301247</v>
+        <v>0.009940357852882704</v>
       </c>
       <c r="U2">
-        <v>51648.2</v>
+        <v>37073.1</v>
       </c>
       <c r="V2">
-        <v>0.8086874693697969</v>
+        <v>0.6352952667862779</v>
       </c>
       <c r="W2">
-        <v>-0.06250749850029994</v>
+        <v>0.0147047818603607</v>
       </c>
       <c r="X2">
-        <v>0.1257048381800152</v>
+        <v>0.1052870499241518</v>
       </c>
       <c r="Y2">
-        <v>-0.1882123366803151</v>
+        <v>-0.09058226806379106</v>
       </c>
       <c r="Z2">
-        <v>0.02217198625935183</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.09105143662412904</v>
+        <v>0.06106347464639409</v>
       </c>
       <c r="AB2">
-        <v>0.09049977469542371</v>
+        <v>0.07682705581879572</v>
       </c>
       <c r="AC2">
-        <v>-0.1815512113195528</v>
+        <v>-0.0151155491482815</v>
       </c>
       <c r="AD2">
-        <v>77762.39999999999</v>
+        <v>58916.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77762.39999999999</v>
+        <v>58916.8</v>
       </c>
       <c r="AG2">
-        <v>26114.19999999999</v>
+        <v>21843.7</v>
       </c>
       <c r="AH2">
-        <v>0.5490566557296488</v>
+        <v>0.5023922914579292</v>
       </c>
       <c r="AI2">
-        <v>0.654984670327819</v>
+        <v>0.6589096309816185</v>
       </c>
       <c r="AJ2">
-        <v>0.2902193687771515</v>
+        <v>0.2723673743195086</v>
       </c>
       <c r="AK2">
-        <v>0.3893237203283448</v>
+        <v>0.4173224435210393</v>
       </c>
       <c r="AL2">
-        <v>1004.8</v>
+        <v>1010.8</v>
       </c>
       <c r="AM2">
-        <v>1004.8</v>
+        <v>1010.8</v>
       </c>
       <c r="AN2">
-        <v>32.06961398878258</v>
+        <v>6.62165078223341</v>
       </c>
       <c r="AO2">
-        <v>2.168988853503185</v>
+        <v>8.198258804907004</v>
       </c>
       <c r="AP2">
-        <v>10.76963048498845</v>
+        <v>2.45501033986693</v>
       </c>
       <c r="AQ2">
-        <v>2.168988853503185</v>
+        <v>8.198258804907004</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prudential plc (LSE:PRU)</t>
+          <t>Phoenix Group Holdings plc (LSE:PHNX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,50 +706,29 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.545</v>
-      </c>
-      <c r="E3">
-        <v>-0.09039999999999999</v>
-      </c>
       <c r="F3">
-        <v>0.09300000000000001</v>
-      </c>
-      <c r="G3">
-        <v>1.641751201281367</v>
-      </c>
-      <c r="H3">
-        <v>1.641751201281367</v>
-      </c>
-      <c r="I3">
-        <v>0.9733048585157501</v>
-      </c>
-      <c r="J3">
-        <v>0.7194743188318674</v>
+        <v>0.111</v>
       </c>
       <c r="K3">
-        <v>2072</v>
-      </c>
-      <c r="L3">
-        <v>1.106246663107314</v>
+        <v>-1017.9</v>
       </c>
       <c r="M3">
-        <v>458</v>
+        <v>682.4</v>
       </c>
       <c r="N3">
-        <v>0.01231772192070399</v>
+        <v>0.100155575777145</v>
       </c>
       <c r="O3">
-        <v>0.221042471042471</v>
+        <v>-0.670399842813636</v>
       </c>
       <c r="P3">
-        <v>458</v>
+        <v>682.4</v>
       </c>
       <c r="Q3">
-        <v>0.01231772192070399</v>
+        <v>0.100155575777145</v>
       </c>
       <c r="R3">
-        <v>0.221042471042471</v>
+        <v>-0.670399842813636</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +737,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6415</v>
+        <v>10236.2</v>
       </c>
       <c r="V3">
-        <v>0.1725287906578954</v>
+        <v>1.502362990577392</v>
       </c>
       <c r="W3">
-        <v>0.1318653344364539</v>
+        <v>-0.1490009514747859</v>
       </c>
       <c r="X3">
-        <v>0.1012288982310274</v>
+        <v>0.1052870499241518</v>
       </c>
       <c r="Y3">
-        <v>0.03063643620542647</v>
-      </c>
-      <c r="Z3">
-        <v>0.115710137764873</v>
-      </c>
-      <c r="AA3">
-        <v>0.08325047255032357</v>
+        <v>-0.2542880013989377</v>
       </c>
       <c r="AB3">
-        <v>0.09354151678189768</v>
-      </c>
-      <c r="AC3">
-        <v>-0.01029104423157411</v>
+        <v>0.07682705581879572</v>
       </c>
       <c r="AD3">
-        <v>5919</v>
+        <v>5083.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5919</v>
+        <v>5083.2</v>
       </c>
       <c r="AG3">
-        <v>-496</v>
+        <v>-5153.000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1373279630265515</v>
+        <v>0.427281744363936</v>
       </c>
       <c r="AI3">
-        <v>0.2667297553062052</v>
+        <v>0.5132834509708886</v>
       </c>
       <c r="AJ3">
-        <v>-0.01352007021713887</v>
+        <v>-3.103469043603954</v>
       </c>
       <c r="AK3">
-        <v>-0.03144016227180527</v>
+        <v>15.47912285971761</v>
       </c>
       <c r="AL3">
-        <v>267</v>
+        <v>315.2</v>
       </c>
       <c r="AM3">
-        <v>267</v>
+        <v>315.2</v>
       </c>
       <c r="AN3">
-        <v>3.175429184549356</v>
+        <v>7.766539343009931</v>
       </c>
       <c r="AO3">
-        <v>6.827715355805243</v>
+        <v>1.951459390862944</v>
       </c>
       <c r="AP3">
-        <v>-0.2660944206008584</v>
+        <v>-7.873185637891521</v>
       </c>
       <c r="AQ3">
-        <v>6.827715355805243</v>
+        <v>1.951459390862944</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +805,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
+          <t>Prudential plc (LSE:PRU)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,106 +814,106 @@
         </is>
       </c>
       <c r="E4">
-        <v>0.0684</v>
+        <v>0.0393</v>
       </c>
       <c r="F4">
-        <v>0.04480000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="K4">
-        <v>2598</v>
+        <v>3450</v>
       </c>
       <c r="M4">
-        <v>1444.8</v>
+        <v>515</v>
       </c>
       <c r="N4">
-        <v>0.08104060443905971</v>
+        <v>0.01662657992865099</v>
       </c>
       <c r="O4">
-        <v>0.5561200923787529</v>
+        <v>0.1492753623188406</v>
       </c>
       <c r="P4">
-        <v>1371.9</v>
+        <v>515</v>
       </c>
       <c r="Q4">
-        <v>0.07695155400743771</v>
+        <v>0.01662657992865099</v>
       </c>
       <c r="R4">
-        <v>0.5280600461893765</v>
+        <v>0.1492753623188406</v>
       </c>
       <c r="S4">
-        <v>72.90000000000009</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.0504568106312293</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>30103.9</v>
+        <v>5920</v>
       </c>
       <c r="V4">
-        <v>1.688564681598151</v>
+        <v>0.1911249576264346</v>
       </c>
       <c r="W4">
-        <v>0.181800369478811</v>
+        <v>0.2141659941647526</v>
       </c>
       <c r="X4">
-        <v>0.2446460460594309</v>
+        <v>0.08697361708147765</v>
       </c>
       <c r="Y4">
-        <v>-0.06284567658061996</v>
+        <v>0.127192377083275</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.04464741953402325</v>
+        <v>0.2365485259506999</v>
       </c>
       <c r="AB4">
-        <v>0.08871137804719656</v>
+        <v>0.0803363203643648</v>
       </c>
       <c r="AC4">
-        <v>-0.04406395851317331</v>
+        <v>0.1562122055863351</v>
       </c>
       <c r="AD4">
-        <v>63966.2</v>
+        <v>5368</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>63966.2</v>
+        <v>5368</v>
       </c>
       <c r="AG4">
-        <v>33862.3</v>
+        <v>-552</v>
       </c>
       <c r="AH4">
-        <v>0.7820373791327758</v>
+        <v>0.1477058540276536</v>
       </c>
       <c r="AI4">
-        <v>0.8188816103622778</v>
+        <v>0.2366947396269677</v>
       </c>
       <c r="AJ4">
-        <v>0.6550984322040456</v>
+        <v>-0.01814446544498315</v>
       </c>
       <c r="AK4">
-        <v>0.7053147039587421</v>
+        <v>-0.03293752610537622</v>
       </c>
       <c r="AL4">
-        <v>275.8</v>
+        <v>182</v>
       </c>
       <c r="AM4">
-        <v>275.8</v>
+        <v>182</v>
       </c>
       <c r="AN4">
-        <v>16.7564834704249</v>
+        <v>1.162156310889803</v>
       </c>
       <c r="AO4">
-        <v>13.22661348803481</v>
+        <v>22.42307692307692</v>
       </c>
       <c r="AP4">
-        <v>8.870513962382772</v>
+        <v>-0.11950638666378</v>
       </c>
       <c r="AQ4">
-        <v>13.22661348803481</v>
+        <v>22.42307692307692</v>
       </c>
     </row>
     <row r="5">
@@ -980,122 +932,107 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.598</v>
+      <c r="E5">
+        <v>-0.266</v>
       </c>
       <c r="F5">
-        <v>0.0958</v>
-      </c>
-      <c r="G5">
-        <v>5.034700315457413</v>
-      </c>
-      <c r="H5">
-        <v>5.034700315457413</v>
-      </c>
-      <c r="I5">
-        <v>-3.668769716088328</v>
-      </c>
-      <c r="J5">
-        <v>-3.668769716088328</v>
+        <v>0.103</v>
       </c>
       <c r="K5">
-        <v>-208.4</v>
-      </c>
-      <c r="L5">
-        <v>-6.574132492113565</v>
+        <v>39.3</v>
       </c>
       <c r="M5">
-        <v>462.7</v>
+        <v>43.6</v>
       </c>
       <c r="N5">
-        <v>0.4531387719126432</v>
+        <v>0.03836339639243291</v>
       </c>
       <c r="O5">
-        <v>-2.220249520153551</v>
+        <v>1.10941475826972</v>
       </c>
       <c r="P5">
-        <v>36.7</v>
+        <v>43.6</v>
       </c>
       <c r="Q5">
-        <v>0.03594163157379297</v>
+        <v>0.03836339639243291</v>
       </c>
       <c r="R5">
-        <v>-0.1761036468330134</v>
+        <v>1.10941475826972</v>
       </c>
       <c r="S5">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.9206829479144154</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1826.5</v>
+        <v>2260</v>
       </c>
       <c r="V5">
-        <v>1.788757222603075</v>
+        <v>1.988561372635284</v>
       </c>
       <c r="W5">
-        <v>-0.06250749850029994</v>
+        <v>0.0147047818603607</v>
       </c>
       <c r="X5">
-        <v>0.1831866056932369</v>
+        <v>0.2255148928054609</v>
       </c>
       <c r="Y5">
-        <v>-0.2456941041935368</v>
+        <v>-0.2108101109451002</v>
       </c>
       <c r="Z5">
-        <v>0.02481797541689502</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.09105143662412904</v>
+        <v>0.06106347464639409</v>
       </c>
       <c r="AB5">
-        <v>0.09049977469542371</v>
+        <v>0.07617902379467559</v>
       </c>
       <c r="AC5">
-        <v>-0.1815512113195528</v>
+        <v>-0.0151155491482815</v>
       </c>
       <c r="AD5">
-        <v>2163.3</v>
+        <v>5121.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2163.3</v>
+        <v>5121.3</v>
       </c>
       <c r="AG5">
-        <v>336.8000000000002</v>
+        <v>2861.3</v>
       </c>
       <c r="AH5">
-        <v>0.6793430473558598</v>
+        <v>0.8183866534564863</v>
       </c>
       <c r="AI5">
-        <v>0.4475916577009021</v>
+        <v>0.7751089720305121</v>
       </c>
       <c r="AJ5">
-        <v>0.2480300463951691</v>
+        <v>0.7157186452548902</v>
       </c>
       <c r="AK5">
-        <v>0.1120164964911698</v>
+        <v>0.6581937799043062</v>
       </c>
       <c r="AL5">
-        <v>163.7</v>
+        <v>181.3</v>
       </c>
       <c r="AM5">
-        <v>163.7</v>
+        <v>181.3</v>
       </c>
       <c r="AN5">
-        <v>-18.79496090356212</v>
+        <v>22.65059708093764</v>
       </c>
       <c r="AO5">
-        <v>-0.710445937690898</v>
+        <v>1.227799227799228</v>
       </c>
       <c r="AP5">
-        <v>-2.926151172893138</v>
+        <v>12.65501990269792</v>
       </c>
       <c r="AQ5">
-        <v>-0.710445937690898</v>
+        <v>1.227799227799228</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1043,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chesnara plc (LSE:CSN)</t>
+          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1114,101 +1051,107 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="E6">
+        <v>0.0344</v>
+      </c>
+      <c r="F6">
+        <v>0.0791</v>
+      </c>
       <c r="K6">
-        <v>-71.40000000000001</v>
+        <v>2582.3</v>
       </c>
       <c r="M6">
-        <v>41.306</v>
+        <v>1531.3</v>
       </c>
       <c r="N6">
-        <v>0.08042445482866044</v>
+        <v>0.08089404480789447</v>
       </c>
       <c r="O6">
-        <v>-0.578515406162465</v>
+        <v>0.592998489718468</v>
       </c>
       <c r="P6">
-        <v>41.2</v>
+        <v>1503.3</v>
       </c>
       <c r="Q6">
-        <v>0.08021806853582555</v>
+        <v>0.07941488771612862</v>
       </c>
       <c r="R6">
-        <v>-0.5770308123249299</v>
+        <v>0.5821554428222901</v>
       </c>
       <c r="S6">
-        <v>0.1060000000000016</v>
+        <v>28</v>
       </c>
       <c r="T6">
-        <v>0.002566213140948086</v>
+        <v>0.01828511722066218</v>
       </c>
       <c r="U6">
-        <v>254.6</v>
+        <v>18473.5</v>
       </c>
       <c r="V6">
-        <v>0.4957165109034268</v>
+        <v>0.975900304812015</v>
       </c>
       <c r="W6">
-        <v>-0.1104921077065924</v>
+        <v>0.1819597508385242</v>
       </c>
       <c r="X6">
-        <v>0.1160706332365033</v>
+        <v>0.1541924427713359</v>
       </c>
       <c r="Y6">
-        <v>-0.2265627409430957</v>
+        <v>0.0277673080671883</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.1892455858747993</v>
+        <v>0.06076279205534025</v>
       </c>
       <c r="AB6">
-        <v>0.09057541633748657</v>
+        <v>0.07627733582451271</v>
       </c>
       <c r="AC6">
-        <v>-0.2798210022122859</v>
+        <v>-0.01551454376917246</v>
       </c>
       <c r="AD6">
-        <v>264</v>
+        <v>43076.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>264</v>
+        <v>43076.1</v>
       </c>
       <c r="AG6">
-        <v>9.400000000000006</v>
+        <v>24602.6</v>
       </c>
       <c r="AH6">
-        <v>0.3395061728395062</v>
+        <v>0.6947108173751487</v>
       </c>
       <c r="AI6">
-        <v>0.3699033207229928</v>
+        <v>0.8702699535733189</v>
       </c>
       <c r="AJ6">
-        <v>0.01797323135755259</v>
+        <v>0.5651573659099105</v>
       </c>
       <c r="AK6">
-        <v>0.02047484208233501</v>
+        <v>0.7930208645592591</v>
       </c>
       <c r="AL6">
-        <v>12.7</v>
+        <v>317.7</v>
       </c>
       <c r="AM6">
-        <v>12.7</v>
+        <v>317.7</v>
       </c>
       <c r="AN6">
-        <v>-2.256410256410256</v>
+        <v>12.3870884255931</v>
       </c>
       <c r="AO6">
-        <v>-9.283464566929135</v>
+        <v>10.86402266288952</v>
       </c>
       <c r="AP6">
-        <v>-0.08034188034188039</v>
+        <v>7.074795111430625</v>
       </c>
       <c r="AQ6">
-        <v>-9.283464566929135</v>
+        <v>10.86402266288952</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1162,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phoenix Group Holdings plc (LSE:PHNX)</t>
+          <t>Chesnara plc (LSE:CSN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1227,29 +1170,26 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="F7">
-        <v>-0.027</v>
-      </c>
       <c r="K7">
-        <v>-1246.7</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="M7">
-        <v>629.4</v>
+        <v>44.5</v>
       </c>
       <c r="N7">
-        <v>0.08596364232350411</v>
+        <v>0.08871610845295055</v>
       </c>
       <c r="O7">
-        <v>-0.5048528114221544</v>
+        <v>-0.6856702619414483</v>
       </c>
       <c r="P7">
-        <v>629.4</v>
+        <v>44.5</v>
       </c>
       <c r="Q7">
-        <v>0.08596364232350411</v>
+        <v>0.08871610845295055</v>
       </c>
       <c r="R7">
-        <v>-0.5048528114221544</v>
+        <v>-0.6856702619414483</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,73 +1198,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>13048.2</v>
+        <v>183.4</v>
       </c>
       <c r="V7">
-        <v>1.782127101629403</v>
+        <v>0.3656299840510367</v>
       </c>
       <c r="W7">
-        <v>-0.1369352943114792</v>
+        <v>-0.1443184345118968</v>
       </c>
       <c r="X7">
-        <v>0.1257048381800152</v>
+        <v>0.09852864173736108</v>
       </c>
       <c r="Y7">
-        <v>-0.2626401324914944</v>
+        <v>-0.2428470762492579</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>-1.203756201275691</v>
+        <v>-0.1816597691134829</v>
       </c>
       <c r="AB7">
-        <v>0.08954917188445799</v>
+        <v>0.07767722997050652</v>
       </c>
       <c r="AC7">
-        <v>-1.293305373160149</v>
+        <v>-0.2593369990839894</v>
       </c>
       <c r="AD7">
-        <v>5449.9</v>
+        <v>268.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>5449.9</v>
+        <v>268.2</v>
       </c>
       <c r="AG7">
-        <v>-7598.300000000001</v>
+        <v>84.79999999999998</v>
       </c>
       <c r="AH7">
-        <v>0.4267202229947696</v>
+        <v>0.3484021823850351</v>
       </c>
       <c r="AI7">
-        <v>0.4233918582970789</v>
+        <v>0.3680526965829559</v>
       </c>
       <c r="AJ7">
-        <v>27.47035430224138</v>
+        <v>0.1446111869031378</v>
       </c>
       <c r="AK7">
-        <v>43.12315550510766</v>
+        <v>0.1555107280396112</v>
       </c>
       <c r="AL7">
-        <v>285.6</v>
+        <v>14.6</v>
       </c>
       <c r="AM7">
-        <v>285.6</v>
+        <v>14.6</v>
       </c>
       <c r="AN7">
-        <v>-1.801917672342536</v>
+        <v>-3.373584905660377</v>
       </c>
       <c r="AO7">
-        <v>-10.70483193277311</v>
+        <v>-5.712328767123288</v>
       </c>
       <c r="AP7">
-        <v>2.512249958670855</v>
+        <v>-1.066666666666666</v>
       </c>
       <c r="AQ7">
-        <v>-10.70483193277311</v>
+        <v>-5.712328767123288</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,107 +587,125 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.11</v>
+      </c>
       <c r="E2">
-        <v>0.0344</v>
+        <v>-0.309</v>
       </c>
       <c r="F2">
-        <v>0.107</v>
+        <v>0.0472</v>
+      </c>
+      <c r="G2">
+        <v>0.1219891319707617</v>
+      </c>
+      <c r="H2">
+        <v>0.1219891319707617</v>
+      </c>
+      <c r="I2">
+        <v>0.1194070115488869</v>
+      </c>
+      <c r="J2">
+        <v>0.1194070115488869</v>
       </c>
       <c r="K2">
-        <v>4988.8</v>
+        <v>382.9</v>
+      </c>
+      <c r="L2">
+        <v>0.02459437585910101</v>
       </c>
       <c r="M2">
-        <v>2816.8</v>
+        <v>1612.6</v>
       </c>
       <c r="N2">
-        <v>0.04826949209760143</v>
+        <v>0.09613401293630214</v>
       </c>
       <c r="O2">
-        <v>0.5646247594611929</v>
+        <v>4.211543483938366</v>
       </c>
       <c r="P2">
-        <v>2788.8</v>
+        <v>1570.9</v>
       </c>
       <c r="Q2">
-        <v>0.04778967607277438</v>
+        <v>0.09364809681361591</v>
       </c>
       <c r="R2">
-        <v>0.5590121872995509</v>
+        <v>4.102637764429355</v>
       </c>
       <c r="S2">
-        <v>28</v>
+        <v>41.70000000000005</v>
       </c>
       <c r="T2">
-        <v>0.009940357852882704</v>
+        <v>0.02585886146595563</v>
       </c>
       <c r="U2">
-        <v>37073.1</v>
+        <v>19975.5</v>
       </c>
       <c r="V2">
-        <v>0.6352952667862779</v>
+        <v>1.190825359921309</v>
       </c>
       <c r="W2">
-        <v>0.0147047818603607</v>
+        <v>0.05921927681029416</v>
       </c>
       <c r="X2">
-        <v>0.1052870499241518</v>
+        <v>0.1496112984283135</v>
       </c>
       <c r="Y2">
-        <v>-0.09058226806379106</v>
+        <v>-0.09039202161801932</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.502566320832069</v>
       </c>
       <c r="AA2">
-        <v>0.06106347464639409</v>
+        <v>0.06000994247567644</v>
       </c>
       <c r="AB2">
-        <v>0.07682705581879572</v>
+        <v>0.07853311221303486</v>
       </c>
       <c r="AC2">
-        <v>-0.0151155491482815</v>
+        <v>-0.01852316973735842</v>
       </c>
       <c r="AD2">
-        <v>58916.8</v>
+        <v>35745.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>58916.8</v>
+        <v>35745.1</v>
       </c>
       <c r="AG2">
-        <v>21843.7</v>
+        <v>15769.6</v>
       </c>
       <c r="AH2">
-        <v>0.5023922914579292</v>
+        <v>0.680604955102476</v>
       </c>
       <c r="AI2">
-        <v>0.6589096309816185</v>
+        <v>0.8784392847663891</v>
       </c>
       <c r="AJ2">
-        <v>0.2723673743195086</v>
+        <v>0.4845609496037684</v>
       </c>
       <c r="AK2">
-        <v>0.4173224435210393</v>
+        <v>0.7612243617283175</v>
       </c>
       <c r="AL2">
-        <v>1010.8</v>
+        <v>457.5</v>
       </c>
       <c r="AM2">
-        <v>1010.8</v>
+        <v>457.5</v>
       </c>
       <c r="AN2">
-        <v>6.62165078223341</v>
+        <v>18.99516420448507</v>
       </c>
       <c r="AO2">
-        <v>8.198258804907004</v>
+        <v>4.063387978142076</v>
       </c>
       <c r="AP2">
-        <v>2.45501033986693</v>
+        <v>8.380061643107663</v>
       </c>
       <c r="AQ2">
-        <v>8.198258804907004</v>
+        <v>4.063387978142076</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phoenix Group Holdings plc (LSE:PHNX)</t>
+          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -706,565 +724,125 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.11</v>
+      </c>
+      <c r="E3">
+        <v>-0.309</v>
+      </c>
       <c r="F3">
-        <v>0.111</v>
+        <v>0.0472</v>
+      </c>
+      <c r="G3">
+        <v>0.1219891319707617</v>
+      </c>
+      <c r="H3">
+        <v>0.1219891319707617</v>
+      </c>
+      <c r="I3">
+        <v>0.1194070115488869</v>
+      </c>
+      <c r="J3">
+        <v>0.1194070115488869</v>
       </c>
       <c r="K3">
-        <v>-1017.9</v>
+        <v>382.9</v>
+      </c>
+      <c r="L3">
+        <v>0.02459437585910101</v>
       </c>
       <c r="M3">
-        <v>682.4</v>
+        <v>1612.6</v>
       </c>
       <c r="N3">
-        <v>0.100155575777145</v>
+        <v>0.09613401293630214</v>
       </c>
       <c r="O3">
-        <v>-0.670399842813636</v>
+        <v>4.211543483938366</v>
       </c>
       <c r="P3">
-        <v>682.4</v>
+        <v>1570.9</v>
       </c>
       <c r="Q3">
-        <v>0.100155575777145</v>
+        <v>0.09364809681361591</v>
       </c>
       <c r="R3">
-        <v>-0.670399842813636</v>
+        <v>4.102637764429355</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>41.70000000000005</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.02585886146595563</v>
       </c>
       <c r="U3">
-        <v>10236.2</v>
+        <v>19975.5</v>
       </c>
       <c r="V3">
-        <v>1.502362990577392</v>
+        <v>1.190825359921309</v>
       </c>
       <c r="W3">
-        <v>-0.1490009514747859</v>
+        <v>0.05921927681029416</v>
       </c>
       <c r="X3">
-        <v>0.1052870499241518</v>
+        <v>0.1496112984283135</v>
       </c>
       <c r="Y3">
-        <v>-0.2542880013989377</v>
+        <v>-0.09039202161801932</v>
+      </c>
+      <c r="Z3">
+        <v>0.502566320832069</v>
+      </c>
+      <c r="AA3">
+        <v>0.06000994247567644</v>
       </c>
       <c r="AB3">
-        <v>0.07682705581879572</v>
+        <v>0.07853311221303486</v>
+      </c>
+      <c r="AC3">
+        <v>-0.01852316973735842</v>
       </c>
       <c r="AD3">
-        <v>5083.2</v>
+        <v>35745.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5083.2</v>
+        <v>35745.1</v>
       </c>
       <c r="AG3">
-        <v>-5153.000000000001</v>
+        <v>15769.6</v>
       </c>
       <c r="AH3">
-        <v>0.427281744363936</v>
+        <v>0.680604955102476</v>
       </c>
       <c r="AI3">
-        <v>0.5132834509708886</v>
+        <v>0.8784392847663891</v>
       </c>
       <c r="AJ3">
-        <v>-3.103469043603954</v>
+        <v>0.4845609496037684</v>
       </c>
       <c r="AK3">
-        <v>15.47912285971761</v>
+        <v>0.7612243617283175</v>
       </c>
       <c r="AL3">
-        <v>315.2</v>
+        <v>457.5</v>
       </c>
       <c r="AM3">
-        <v>315.2</v>
+        <v>457.5</v>
       </c>
       <c r="AN3">
-        <v>7.766539343009931</v>
+        <v>18.99516420448507</v>
       </c>
       <c r="AO3">
-        <v>1.951459390862944</v>
+        <v>4.063387978142076</v>
       </c>
       <c r="AP3">
-        <v>-7.873185637891521</v>
+        <v>8.380061643107663</v>
       </c>
       <c r="AQ3">
-        <v>1.951459390862944</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Prudential plc (LSE:PRU)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="E4">
-        <v>0.0393</v>
-      </c>
-      <c r="F4">
-        <v>0.114</v>
-      </c>
-      <c r="K4">
-        <v>3450</v>
-      </c>
-      <c r="M4">
-        <v>515</v>
-      </c>
-      <c r="N4">
-        <v>0.01662657992865099</v>
-      </c>
-      <c r="O4">
-        <v>0.1492753623188406</v>
-      </c>
-      <c r="P4">
-        <v>515</v>
-      </c>
-      <c r="Q4">
-        <v>0.01662657992865099</v>
-      </c>
-      <c r="R4">
-        <v>0.1492753623188406</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>5920</v>
-      </c>
-      <c r="V4">
-        <v>0.1911249576264346</v>
-      </c>
-      <c r="W4">
-        <v>0.2141659941647526</v>
-      </c>
-      <c r="X4">
-        <v>0.08697361708147765</v>
-      </c>
-      <c r="Y4">
-        <v>0.127192377083275</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0.2365485259506999</v>
-      </c>
-      <c r="AB4">
-        <v>0.0803363203643648</v>
-      </c>
-      <c r="AC4">
-        <v>0.1562122055863351</v>
-      </c>
-      <c r="AD4">
-        <v>5368</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>5368</v>
-      </c>
-      <c r="AG4">
-        <v>-552</v>
-      </c>
-      <c r="AH4">
-        <v>0.1477058540276536</v>
-      </c>
-      <c r="AI4">
-        <v>0.2366947396269677</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.01814446544498315</v>
-      </c>
-      <c r="AK4">
-        <v>-0.03293752610537622</v>
-      </c>
-      <c r="AL4">
-        <v>182</v>
-      </c>
-      <c r="AM4">
-        <v>182</v>
-      </c>
-      <c r="AN4">
-        <v>1.162156310889803</v>
-      </c>
-      <c r="AO4">
-        <v>22.42307692307692</v>
-      </c>
-      <c r="AP4">
-        <v>-0.11950638666378</v>
-      </c>
-      <c r="AQ4">
-        <v>22.42307692307692</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Just Group plc (LSE:JUST)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="E5">
-        <v>-0.266</v>
-      </c>
-      <c r="F5">
-        <v>0.103</v>
-      </c>
-      <c r="K5">
-        <v>39.3</v>
-      </c>
-      <c r="M5">
-        <v>43.6</v>
-      </c>
-      <c r="N5">
-        <v>0.03836339639243291</v>
-      </c>
-      <c r="O5">
-        <v>1.10941475826972</v>
-      </c>
-      <c r="P5">
-        <v>43.6</v>
-      </c>
-      <c r="Q5">
-        <v>0.03836339639243291</v>
-      </c>
-      <c r="R5">
-        <v>1.10941475826972</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2260</v>
-      </c>
-      <c r="V5">
-        <v>1.988561372635284</v>
-      </c>
-      <c r="W5">
-        <v>0.0147047818603607</v>
-      </c>
-      <c r="X5">
-        <v>0.2255148928054609</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2108101109451002</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0.06106347464639409</v>
-      </c>
-      <c r="AB5">
-        <v>0.07617902379467559</v>
-      </c>
-      <c r="AC5">
-        <v>-0.0151155491482815</v>
-      </c>
-      <c r="AD5">
-        <v>5121.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>5121.3</v>
-      </c>
-      <c r="AG5">
-        <v>2861.3</v>
-      </c>
-      <c r="AH5">
-        <v>0.8183866534564863</v>
-      </c>
-      <c r="AI5">
-        <v>0.7751089720305121</v>
-      </c>
-      <c r="AJ5">
-        <v>0.7157186452548902</v>
-      </c>
-      <c r="AK5">
-        <v>0.6581937799043062</v>
-      </c>
-      <c r="AL5">
-        <v>181.3</v>
-      </c>
-      <c r="AM5">
-        <v>181.3</v>
-      </c>
-      <c r="AN5">
-        <v>22.65059708093764</v>
-      </c>
-      <c r="AO5">
-        <v>1.227799227799228</v>
-      </c>
-      <c r="AP5">
-        <v>12.65501990269792</v>
-      </c>
-      <c r="AQ5">
-        <v>1.227799227799228</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="E6">
-        <v>0.0344</v>
-      </c>
-      <c r="F6">
-        <v>0.0791</v>
-      </c>
-      <c r="K6">
-        <v>2582.3</v>
-      </c>
-      <c r="M6">
-        <v>1531.3</v>
-      </c>
-      <c r="N6">
-        <v>0.08089404480789447</v>
-      </c>
-      <c r="O6">
-        <v>0.592998489718468</v>
-      </c>
-      <c r="P6">
-        <v>1503.3</v>
-      </c>
-      <c r="Q6">
-        <v>0.07941488771612862</v>
-      </c>
-      <c r="R6">
-        <v>0.5821554428222901</v>
-      </c>
-      <c r="S6">
-        <v>28</v>
-      </c>
-      <c r="T6">
-        <v>0.01828511722066218</v>
-      </c>
-      <c r="U6">
-        <v>18473.5</v>
-      </c>
-      <c r="V6">
-        <v>0.975900304812015</v>
-      </c>
-      <c r="W6">
-        <v>0.1819597508385242</v>
-      </c>
-      <c r="X6">
-        <v>0.1541924427713359</v>
-      </c>
-      <c r="Y6">
-        <v>0.0277673080671883</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0.06076279205534025</v>
-      </c>
-      <c r="AB6">
-        <v>0.07627733582451271</v>
-      </c>
-      <c r="AC6">
-        <v>-0.01551454376917246</v>
-      </c>
-      <c r="AD6">
-        <v>43076.1</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>43076.1</v>
-      </c>
-      <c r="AG6">
-        <v>24602.6</v>
-      </c>
-      <c r="AH6">
-        <v>0.6947108173751487</v>
-      </c>
-      <c r="AI6">
-        <v>0.8702699535733189</v>
-      </c>
-      <c r="AJ6">
-        <v>0.5651573659099105</v>
-      </c>
-      <c r="AK6">
-        <v>0.7930208645592591</v>
-      </c>
-      <c r="AL6">
-        <v>317.7</v>
-      </c>
-      <c r="AM6">
-        <v>317.7</v>
-      </c>
-      <c r="AN6">
-        <v>12.3870884255931</v>
-      </c>
-      <c r="AO6">
-        <v>10.86402266288952</v>
-      </c>
-      <c r="AP6">
-        <v>7.074795111430625</v>
-      </c>
-      <c r="AQ6">
-        <v>10.86402266288952</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Chesnara plc (LSE:CSN)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="K7">
-        <v>-64.90000000000001</v>
-      </c>
-      <c r="M7">
-        <v>44.5</v>
-      </c>
-      <c r="N7">
-        <v>0.08871610845295055</v>
-      </c>
-      <c r="O7">
-        <v>-0.6856702619414483</v>
-      </c>
-      <c r="P7">
-        <v>44.5</v>
-      </c>
-      <c r="Q7">
-        <v>0.08871610845295055</v>
-      </c>
-      <c r="R7">
-        <v>-0.6856702619414483</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>183.4</v>
-      </c>
-      <c r="V7">
-        <v>0.3656299840510367</v>
-      </c>
-      <c r="W7">
-        <v>-0.1443184345118968</v>
-      </c>
-      <c r="X7">
-        <v>0.09852864173736108</v>
-      </c>
-      <c r="Y7">
-        <v>-0.2428470762492579</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>-0.1816597691134829</v>
-      </c>
-      <c r="AB7">
-        <v>0.07767722997050652</v>
-      </c>
-      <c r="AC7">
-        <v>-0.2593369990839894</v>
-      </c>
-      <c r="AD7">
-        <v>268.2</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>268.2</v>
-      </c>
-      <c r="AG7">
-        <v>84.79999999999998</v>
-      </c>
-      <c r="AH7">
-        <v>0.3484021823850351</v>
-      </c>
-      <c r="AI7">
-        <v>0.3680526965829559</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1446111869031378</v>
-      </c>
-      <c r="AK7">
-        <v>0.1555107280396112</v>
-      </c>
-      <c r="AL7">
-        <v>14.6</v>
-      </c>
-      <c r="AM7">
-        <v>14.6</v>
-      </c>
-      <c r="AN7">
-        <v>-3.373584905660377</v>
-      </c>
-      <c r="AO7">
-        <v>-5.712328767123288</v>
-      </c>
-      <c r="AP7">
-        <v>-1.066666666666666</v>
-      </c>
-      <c r="AQ7">
-        <v>-5.712328767123288</v>
+        <v>4.063387978142076</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.11</v>
+        <v>-0.0688</v>
       </c>
       <c r="E2">
-        <v>-0.309</v>
+        <v>-0.347</v>
       </c>
       <c r="F2">
-        <v>0.0472</v>
+        <v>0.1016</v>
       </c>
       <c r="G2">
-        <v>0.1219891319707617</v>
+        <v>0.1961232092258307</v>
       </c>
       <c r="H2">
-        <v>0.1219891319707617</v>
+        <v>0.1961232092258307</v>
       </c>
       <c r="I2">
-        <v>0.1194070115488869</v>
+        <v>0.1942690272851566</v>
       </c>
       <c r="J2">
-        <v>0.1194070115488869</v>
+        <v>0.1807218415378686</v>
       </c>
       <c r="K2">
-        <v>382.9</v>
+        <v>516.8199999999999</v>
       </c>
       <c r="L2">
-        <v>0.02459437585910101</v>
+        <v>0.02560187845522817</v>
       </c>
       <c r="M2">
-        <v>1612.6</v>
+        <v>1706.2</v>
       </c>
       <c r="N2">
-        <v>0.09613401293630214</v>
+        <v>0.0880106054275442</v>
       </c>
       <c r="O2">
-        <v>4.211543483938366</v>
+        <v>3.301342827289966</v>
       </c>
       <c r="P2">
-        <v>1570.9</v>
+        <v>1664.5</v>
       </c>
       <c r="Q2">
-        <v>0.09364809681361591</v>
+        <v>0.08585960188380455</v>
       </c>
       <c r="R2">
-        <v>4.102637764429355</v>
+        <v>3.220657095313649</v>
       </c>
       <c r="S2">
         <v>41.70000000000005</v>
       </c>
       <c r="T2">
-        <v>0.02585886146595563</v>
+        <v>0.02444027663814327</v>
       </c>
       <c r="U2">
-        <v>19975.5</v>
+        <v>22720.6</v>
       </c>
       <c r="V2">
-        <v>1.190825359921309</v>
+        <v>1.171992592707221</v>
       </c>
       <c r="W2">
         <v>0.05921927681029416</v>
       </c>
       <c r="X2">
-        <v>0.1496112984283135</v>
+        <v>0.1495628175284777</v>
       </c>
       <c r="Y2">
-        <v>-0.09039202161801932</v>
+        <v>-0.09034354071818354</v>
       </c>
       <c r="Z2">
-        <v>0.502566320832069</v>
+        <v>0.5627092375321608</v>
       </c>
       <c r="AA2">
         <v>0.06000994247567644</v>
       </c>
       <c r="AB2">
-        <v>0.07853311221303486</v>
+        <v>0.07877454379012067</v>
       </c>
       <c r="AC2">
-        <v>-0.01852316973735842</v>
+        <v>-0.01850768517817869</v>
       </c>
       <c r="AD2">
-        <v>35745.1</v>
+        <v>41086.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>35745.1</v>
+        <v>41086.3</v>
       </c>
       <c r="AG2">
-        <v>15769.6</v>
+        <v>18365.7</v>
       </c>
       <c r="AH2">
-        <v>0.680604955102476</v>
+        <v>0.6794201010044219</v>
       </c>
       <c r="AI2">
-        <v>0.8784392847663891</v>
+        <v>0.8558825612545464</v>
       </c>
       <c r="AJ2">
-        <v>0.4845609496037684</v>
+        <v>0.4864828353464716</v>
       </c>
       <c r="AK2">
-        <v>0.7612243617283175</v>
+        <v>0.7263763644992881</v>
       </c>
       <c r="AL2">
-        <v>457.5</v>
+        <v>2357.1</v>
       </c>
       <c r="AM2">
-        <v>457.5</v>
+        <v>2357.1</v>
       </c>
       <c r="AN2">
-        <v>18.99516420448507</v>
+        <v>10.38791970064725</v>
       </c>
       <c r="AO2">
-        <v>4.063387978142076</v>
+        <v>1.663769038224937</v>
       </c>
       <c r="AP2">
-        <v>8.380061643107663</v>
+        <v>4.643431432038835</v>
       </c>
       <c r="AQ2">
-        <v>4.063387978142076</v>
+        <v>1.663769038224937</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
+          <t>Just Group plc (LSE:JUST)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,392 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.11</v>
-      </c>
-      <c r="E3">
-        <v>-0.309</v>
+        <v>-0.0121</v>
       </c>
       <c r="F3">
-        <v>0.0472</v>
+        <v>0.156</v>
       </c>
       <c r="G3">
-        <v>0.1219891319707617</v>
+        <v>0.4983535380637608</v>
       </c>
       <c r="H3">
-        <v>0.1219891319707617</v>
+        <v>0.4983535380637608</v>
       </c>
       <c r="I3">
-        <v>0.1194070115488869</v>
+        <v>0.5009390931043735</v>
       </c>
       <c r="J3">
-        <v>0.1194070115488869</v>
+        <v>0.3961414055285505</v>
       </c>
       <c r="K3">
-        <v>382.9</v>
+        <v>127.6</v>
       </c>
       <c r="L3">
-        <v>0.02459437585910101</v>
+        <v>0.03112422860209284</v>
       </c>
       <c r="M3">
-        <v>1612.6</v>
+        <v>48</v>
       </c>
       <c r="N3">
-        <v>0.09613401293630214</v>
+        <v>0.02272942513495596</v>
       </c>
       <c r="O3">
-        <v>4.211543483938366</v>
+        <v>0.3761755485893417</v>
       </c>
       <c r="P3">
-        <v>1570.9</v>
+        <v>48</v>
       </c>
       <c r="Q3">
-        <v>0.09364809681361591</v>
+        <v>0.02272942513495596</v>
       </c>
       <c r="R3">
-        <v>4.102637764429355</v>
+        <v>0.3761755485893417</v>
       </c>
       <c r="S3">
-        <v>41.70000000000005</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.02585886146595563</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>19975.5</v>
+        <v>2579.4</v>
       </c>
       <c r="V3">
-        <v>1.190825359921309</v>
+        <v>1.221422483189696</v>
       </c>
       <c r="W3">
-        <v>0.05921927681029416</v>
+        <v>0.08566633098355152</v>
       </c>
       <c r="X3">
-        <v>0.1496112984283135</v>
+        <v>0.1577767671562176</v>
       </c>
       <c r="Y3">
-        <v>-0.09039202161801932</v>
+        <v>-0.07211043617266612</v>
       </c>
       <c r="Z3">
-        <v>0.502566320832069</v>
+        <v>0.9422864760503814</v>
       </c>
       <c r="AA3">
-        <v>0.06000994247567644</v>
+        <v>0.373278689033143</v>
       </c>
       <c r="AB3">
-        <v>0.07853311221303486</v>
+        <v>0.07877454379012067</v>
       </c>
       <c r="AC3">
-        <v>-0.01852316973735842</v>
+        <v>0.2945041452430223</v>
       </c>
       <c r="AD3">
-        <v>35745.1</v>
+        <v>5079.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
+        <v>5079.2</v>
+      </c>
+      <c r="AG3">
+        <v>2499.8</v>
+      </c>
+      <c r="AH3">
+        <v>0.70632735363649</v>
+      </c>
+      <c r="AI3">
+        <v>0.765666219455206</v>
+      </c>
+      <c r="AJ3">
+        <v>0.5420678289530747</v>
+      </c>
+      <c r="AK3">
+        <v>0.6165799274843993</v>
+      </c>
+      <c r="AL3">
+        <v>1885.6</v>
+      </c>
+      <c r="AM3">
+        <v>1885.6</v>
+      </c>
+      <c r="AN3">
+        <v>2.470187724929482</v>
+      </c>
+      <c r="AO3">
+        <v>1.089149342384387</v>
+      </c>
+      <c r="AP3">
+        <v>1.215737768699543</v>
+      </c>
+      <c r="AQ3">
+        <v>1.089149342384387</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Legal &amp; General Group Plc (LSE:LGEN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.11</v>
+      </c>
+      <c r="E4">
+        <v>-0.309</v>
+      </c>
+      <c r="F4">
+        <v>0.0472</v>
+      </c>
+      <c r="G4">
+        <v>0.1219891319707617</v>
+      </c>
+      <c r="H4">
+        <v>0.1219891319707617</v>
+      </c>
+      <c r="I4">
+        <v>0.1194070115488869</v>
+      </c>
+      <c r="J4">
+        <v>0.1194070115488869</v>
+      </c>
+      <c r="K4">
+        <v>382.9</v>
+      </c>
+      <c r="L4">
+        <v>0.02459437585910101</v>
+      </c>
+      <c r="M4">
+        <v>1612.6</v>
+      </c>
+      <c r="N4">
+        <v>0.09613401293630214</v>
+      </c>
+      <c r="O4">
+        <v>4.211543483938366</v>
+      </c>
+      <c r="P4">
+        <v>1570.9</v>
+      </c>
+      <c r="Q4">
+        <v>0.09364809681361591</v>
+      </c>
+      <c r="R4">
+        <v>4.102637764429355</v>
+      </c>
+      <c r="S4">
+        <v>41.70000000000005</v>
+      </c>
+      <c r="T4">
+        <v>0.02585886146595563</v>
+      </c>
+      <c r="U4">
+        <v>19975.5</v>
+      </c>
+      <c r="V4">
+        <v>1.190825359921309</v>
+      </c>
+      <c r="W4">
+        <v>0.05921927681029416</v>
+      </c>
+      <c r="X4">
+        <v>0.1495628175284777</v>
+      </c>
+      <c r="Y4">
+        <v>-0.09034354071818354</v>
+      </c>
+      <c r="Z4">
+        <v>0.502566320832069</v>
+      </c>
+      <c r="AA4">
+        <v>0.06000994247567644</v>
+      </c>
+      <c r="AB4">
+        <v>0.07851762765385513</v>
+      </c>
+      <c r="AC4">
+        <v>-0.01850768517817869</v>
+      </c>
+      <c r="AD4">
         <v>35745.1</v>
       </c>
-      <c r="AG3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>35745.1</v>
+      </c>
+      <c r="AG4">
         <v>15769.6</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.680604955102476</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.8784392847663891</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>0.4845609496037684</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>0.7612243617283175</v>
       </c>
-      <c r="AL3">
+      <c r="AL4">
         <v>457.5</v>
       </c>
-      <c r="AM3">
+      <c r="AM4">
         <v>457.5</v>
       </c>
-      <c r="AN3">
+      <c r="AN4">
         <v>18.99516420448507</v>
       </c>
-      <c r="AO3">
+      <c r="AO4">
         <v>4.063387978142076</v>
       </c>
-      <c r="AP3">
+      <c r="AP4">
         <v>8.380061643107663</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ4">
         <v>4.063387978142076</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Chesnara plc (LSE:CSN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0688</v>
+      </c>
+      <c r="E5">
+        <v>-0.385</v>
+      </c>
+      <c r="G5">
+        <v>0.03240115718418515</v>
+      </c>
+      <c r="H5">
+        <v>0.03240115718418515</v>
+      </c>
+      <c r="I5">
+        <v>0.01729990356798457</v>
+      </c>
+      <c r="J5">
+        <v>0.01729990356798457</v>
+      </c>
+      <c r="K5">
+        <v>6.32</v>
+      </c>
+      <c r="L5">
+        <v>0.01218900675024108</v>
+      </c>
+      <c r="M5">
+        <v>45.6</v>
+      </c>
+      <c r="N5">
+        <v>0.0912</v>
+      </c>
+      <c r="O5">
+        <v>7.215189873417722</v>
+      </c>
+      <c r="P5">
+        <v>45.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.0912</v>
+      </c>
+      <c r="R5">
+        <v>7.215189873417722</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>165.7</v>
+      </c>
+      <c r="V5">
+        <v>0.3314</v>
+      </c>
+      <c r="W5">
+        <v>0.0137242128121607</v>
+      </c>
+      <c r="X5">
+        <v>0.1014316699105818</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08770745709842111</v>
+      </c>
+      <c r="Z5">
+        <v>0.9508527416101228</v>
+      </c>
+      <c r="AA5">
+        <v>0.01644966073720888</v>
+      </c>
+      <c r="AB5">
+        <v>0.08144498704656018</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06499532630935131</v>
+      </c>
+      <c r="AD5">
+        <v>262</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>262</v>
+      </c>
+      <c r="AG5">
+        <v>96.30000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.3438320209973753</v>
+      </c>
+      <c r="AI5">
+        <v>0.3856911526571471</v>
+      </c>
+      <c r="AJ5">
+        <v>0.1614958913298676</v>
+      </c>
+      <c r="AK5">
+        <v>0.1875</v>
+      </c>
+      <c r="AL5">
+        <v>14</v>
+      </c>
+      <c r="AM5">
+        <v>14</v>
+      </c>
+      <c r="AN5">
+        <v>15.23255813953488</v>
+      </c>
+      <c r="AO5">
+        <v>0.6407142857142858</v>
+      </c>
+      <c r="AP5">
+        <v>5.598837209302326</v>
+      </c>
+      <c r="AQ5">
+        <v>0.6407142857142858</v>
       </c>
     </row>
   </sheetData>
